--- a/GourmetProject/GameConfig/Datas/week.xlsx
+++ b/GourmetProject/GameConfig/Datas/week.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,20 +429,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>requiredScore</t>
+          <t>scoreProfileId</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>rewardType</t>
+          <t>rewardPackageId</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>rewardHiddenScore</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>isBoss</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>modifier</t>
         </is>
@@ -461,20 +466,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -482,99 +492,103 @@
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B3" t="n">
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>score_w1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+          <t>reward_w1</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B4" t="n">
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>score_w2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+          <t>reward_w2</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="B5" t="n">
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>score_w3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Dish</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+          <t>reward_w3</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>score_w4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Boss</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+          <t>reward_w4_boss</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>limit_serve</t>
         </is>
@@ -582,99 +596,103 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="B7" t="n">
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>score_w5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+          <t>reward_w5</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>36</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="B8" t="n">
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>score_w6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+          <t>reward_w6</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>44</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="B9" t="n">
+        <v>7</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>score_w7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+          <t>reward_w7</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>52</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="B10" t="n">
+        <v>8</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>score_w8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Boss</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+          <t>reward_w8_boss</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>small_board</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/week.xlsx
+++ b/GourmetProject/GameConfig/Datas/week.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,82 +456,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>周/关卡ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>分数曲线ID</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>奖励包ID</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>奖励隐藏分</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>是否Boss关</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>关卡修饰符</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>score_w1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>reward_w1</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>score_w2</t>
+          <t>score_w1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>reward_w2</t>
+          <t>reward_w1</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -543,20 +555,20 @@
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>score_w3</t>
+          <t>score_w2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>reward_w3</t>
+          <t>reward_w2</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -568,74 +580,74 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>score_w4</t>
+          <t>score_w3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>reward_w4_boss</t>
+          <t>reward_w3</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>limit_serve</t>
-        </is>
-      </c>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>score_w5</t>
+          <t>score_w4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>reward_w5</t>
+          <t>reward_w4_boss</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>limit_serve</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>score_w6</t>
+          <t>score_w5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>reward_w6</t>
+          <t>reward_w5</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -647,20 +659,20 @@
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>score_w7</t>
+          <t>score_w6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>reward_w7</t>
+          <t>reward_w6</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -672,27 +684,52 @@
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>score_w7</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>reward_w7</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>52</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="n">
         <v>8</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>score_w8</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>reward_w8_boss</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E11" t="n">
         <v>60</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>small_board</t>
         </is>
